--- a/LISTAS_ORDENADAS/MI/Tornillos Pitones Arandelas Tuercas/DRYWALL NAC..xlsx
+++ b/LISTAS_ORDENADAS/MI/Tornillos Pitones Arandelas Tuercas/DRYWALL NAC..xlsx
@@ -614,7 +614,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45216.53876575755</v>
+        <v>45266</v>
       </c>
       <c r="F1" s="5" t="n"/>
       <c r="G1" s="5" t="n"/>
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>5294.344</v>
+        <v>4375.491</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="20">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>5898.726</v>
+        <v>4874.98</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" s="20">
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>7358.929</v>
+        <v>6081.759</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" s="20">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>8944.788</v>
+        <v>7392.386</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" s="20">
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>10286.487</v>
+        <v>8501.228999999999</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" s="20">
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>10890.866</v>
+        <v>9000.715</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" s="20">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>15727.269</v>
+        <v>12997.743</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="20">
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>13538.051</v>
+        <v>11188.472</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="20">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>15883.044</v>
+        <v>13126.483</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="20">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>17135.284</v>
+        <v>14161.392</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="20">
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>12659.206</v>
+        <v>10462.154</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="20">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>11785.384</v>
+        <v>9739.986000000001</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="20">
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="D26" s="15" t="n">
-        <v>13828.126</v>
+        <v>11428.204</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="20">
@@ -1013,7 +1013,9 @@
           <t>4 x 41</t>
         </is>
       </c>
-      <c r="D27" s="15" t="n"/>
+      <c r="D27" s="15" t="n">
+        <v>14585.142</v>
+      </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="20">
       <c r="A28" s="16" t="inlineStr">
@@ -1032,7 +1034,7 @@
         </is>
       </c>
       <c r="D28" s="15" t="n">
-        <v>14142.433</v>
+        <v>11687.961</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="20">
@@ -1052,7 +1054,7 @@
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>17067.637</v>
+        <v>14105.485</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="20">
@@ -1072,7 +1074,7 @@
         </is>
       </c>
       <c r="D30" s="15" t="n">
-        <v>21177.369</v>
+        <v>17501.958</v>
       </c>
       <c r="F30" s="21" t="n"/>
     </row>
@@ -1093,7 +1095,7 @@
         </is>
       </c>
       <c r="D31" s="15" t="n">
-        <v>24706.969</v>
+        <v>20418.983</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="20">
@@ -1122,15 +1124,6 @@
       </c>
       <c r="C35" s="5" t="n"/>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
